--- a/data/internalStats2/File1/RPT_RPT4025233122954TF_internalStats2.xlsx
+++ b/data/internalStats2/File1/RPT_RPT4025233122954TF_internalStats2.xlsx
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>53.13747255988357</v>
+        <v>53.13747255988354</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>60151.11517755451</v>
@@ -2270,7 +2270,7 @@
         <v>180.0194875549072</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>296.8492275607926</v>
+        <v>296.8492275607925</v>
       </c>
       <c r="T12" s="168" t="n">
         <v>114906.3122018267</v>
@@ -2596,7 +2596,7 @@
         <v>1182.582051775061</v>
       </c>
       <c r="S25" s="178" t="n">
-        <v>79339.75577026584</v>
+        <v>79339.75577026587</v>
       </c>
       <c r="T25" s="72" t="n">
         <v>34.07302870312816</v>
@@ -2827,13 +2827,13 @@
         <v>0.04804424818931603</v>
       </c>
       <c r="R28" s="185" t="n">
-        <v>605.7455480868618</v>
+        <v>605.745548086862</v>
       </c>
       <c r="S28" s="187" t="n">
         <v>7909.979579883866</v>
       </c>
       <c r="T28" s="84" t="n">
-        <v>9.113706901155732</v>
+        <v>9.11370690115573</v>
       </c>
       <c r="U28" s="188" t="n">
         <v>0.02636867831121224</v>
@@ -2855,7 +2855,7 @@
         <v>3.129787432848779</v>
       </c>
       <c r="AA28" s="189" t="n">
-        <v>0.009055410591358674</v>
+        <v>0.009055410591358672</v>
       </c>
       <c r="AB28" s="190" t="n">
         <v>79098.00518389465</v>
@@ -3011,7 +3011,7 @@
         <v>22.97068657334675</v>
       </c>
       <c r="AA30" s="189" t="n">
-        <v>0.06646106259610474</v>
+        <v>0.06646106259610472</v>
       </c>
       <c r="AB30" s="190" t="n">
         <v>32130.03089909558</v>
@@ -3275,10 +3275,10 @@
         <v>0.02693237909725248</v>
       </c>
       <c r="R34" s="185" t="n">
-        <v>686.7161600642485</v>
+        <v>686.7161600642484</v>
       </c>
       <c r="S34" s="187" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.884314999522</v>
       </c>
       <c r="T34" s="84" t="n">
         <v>4.506520365848544</v>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="187" t="n">
-        <v>3888.543900562526</v>
+        <v>3888.543900562525</v>
       </c>
       <c r="T36" s="84" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
         <v>6.855622252068915</v>
       </c>
       <c r="U38" s="197" t="n">
-        <v>0.01983536444046377</v>
+        <v>0.01983536444046376</v>
       </c>
       <c r="W38" s="184" t="n">
         <v>14</v>
@@ -3660,7 +3660,7 @@
         <v>4.919003304368093</v>
       </c>
       <c r="U39" s="197" t="n">
-        <v>0.0142321469355377</v>
+        <v>0.01423214693553769</v>
       </c>
       <c r="W39" s="184" t="n">
         <v>15</v>
@@ -3751,7 +3751,7 @@
         <v>13.03311468417755</v>
       </c>
       <c r="AA40" s="189" t="n">
-        <v>0.03770869660693535</v>
+        <v>0.03770869660693534</v>
       </c>
       <c r="AB40" s="190" t="n">
         <v>7972.278752690054</v>
@@ -3886,13 +3886,13 @@
         <v>208.4972261860051</v>
       </c>
       <c r="S42" s="187" t="n">
-        <v>5964.419580898265</v>
+        <v>5964.419580898266</v>
       </c>
       <c r="T42" s="84" t="n">
         <v>7.487248693337843</v>
       </c>
       <c r="U42" s="197" t="n">
-        <v>0.02166284853922978</v>
+        <v>0.02166284853922977</v>
       </c>
       <c r="W42" s="184" t="n">
         <v>18</v>
@@ -3991,7 +3991,7 @@
         <v>1.558715639929586</v>
       </c>
       <c r="AA43" s="189" t="n">
-        <v>0.004509830273644902</v>
+        <v>0.004509830273644901</v>
       </c>
       <c r="AB43" s="190" t="n">
         <v>5001.026602080038</v>
@@ -4071,7 +4071,7 @@
         <v>2.411334708752383</v>
       </c>
       <c r="AA44" s="210" t="n">
-        <v>0.00697671210248039</v>
+        <v>0.006976712102480389</v>
       </c>
       <c r="AB44" s="211" t="n">
         <v>4972.608658942901</v>
@@ -6299,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="AB78" s="190" t="n">
-        <v>9267.033172801768</v>
+        <v>9267.033172801766</v>
       </c>
     </row>
     <row r="79">
@@ -7327,7 +7327,7 @@
         <v>0.4350724259601038</v>
       </c>
       <c r="R97" s="176" t="n">
-        <v>1528.42481492836</v>
+        <v>1528.424814928359</v>
       </c>
       <c r="S97" s="178" t="n">
         <v>51536.05404104013</v>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="O147" s="244" t="n">
-        <v>7437.951394213698</v>
+        <v>7437.951394213699</v>
       </c>
       <c r="P147" s="84" t="n">
         <v>9.113706901155732</v>
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="O301" s="244" t="n">
-        <v>7437.951394213698</v>
+        <v>7437.951394213699</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>9.113706901155732</v>
@@ -15377,7 +15377,7 @@
         <v>3.129787432848779</v>
       </c>
       <c r="AN610" s="189" t="n">
-        <v>0.009055410591358674</v>
+        <v>0.009055410591358672</v>
       </c>
       <c r="AO610" s="190" t="n">
         <v>79098.00518389465</v>
@@ -15425,7 +15425,7 @@
         <v>22.97068657334675</v>
       </c>
       <c r="AN612" s="189" t="n">
-        <v>0.06646106259610474</v>
+        <v>0.06646106259610472</v>
       </c>
       <c r="AO612" s="190" t="n">
         <v>32130.03089909558</v>
@@ -15665,7 +15665,7 @@
         <v>13.03311468417755</v>
       </c>
       <c r="AN622" s="189" t="n">
-        <v>0.03770869660693535</v>
+        <v>0.03770869660693534</v>
       </c>
       <c r="AO622" s="190" t="n">
         <v>7972.278752690054</v>
@@ -15737,7 +15737,7 @@
         <v>1.558715639929586</v>
       </c>
       <c r="AN625" s="189" t="n">
-        <v>0.004509830273644902</v>
+        <v>0.004509830273644901</v>
       </c>
       <c r="AO625" s="190" t="n">
         <v>5001.026602080038</v>
@@ -15761,7 +15761,7 @@
         <v>2.411334708752383</v>
       </c>
       <c r="AN626" s="189" t="n">
-        <v>0.00697671210248039</v>
+        <v>0.006976712102480389</v>
       </c>
       <c r="AO626" s="190" t="n">
         <v>4972.608658942901</v>
@@ -15785,7 +15785,7 @@
         <v>4.817242379133649</v>
       </c>
       <c r="AN627" s="189" t="n">
-        <v>0.01393772216071659</v>
+        <v>0.01393772216071658</v>
       </c>
       <c r="AO627" s="190" t="n">
         <v>4899.263446010251</v>
@@ -15881,7 +15881,7 @@
         <v>1.996222777286802</v>
       </c>
       <c r="AN631" s="189" t="n">
-        <v>0.005775669200543988</v>
+        <v>0.005775669200543987</v>
       </c>
       <c r="AO631" s="190" t="n">
         <v>4028.617329027572</v>
@@ -15953,7 +15953,7 @@
         <v>2.994334165930202</v>
       </c>
       <c r="AN634" s="189" t="n">
-        <v>0.008663503800815982</v>
+        <v>0.008663503800815981</v>
       </c>
       <c r="AO634" s="190" t="n">
         <v>3932.175957900711</v>
@@ -15977,7 +15977,7 @@
         <v>3.935202643494474</v>
       </c>
       <c r="AN635" s="189" t="n">
-        <v>0.01138571754843016</v>
+        <v>0.01138571754843015</v>
       </c>
       <c r="AO635" s="190" t="n">
         <v>3867.690306587611</v>
@@ -16025,7 +16025,7 @@
         <v>3.98061334092186</v>
       </c>
       <c r="AN637" s="189" t="n">
-        <v>0.01151710427013817</v>
+        <v>0.01151710427013816</v>
       </c>
       <c r="AO637" s="190" t="n">
         <v>2094.307385111483</v>
@@ -16073,7 +16073,7 @@
         <v>3.070217775316494</v>
       </c>
       <c r="AN639" s="189" t="n">
-        <v>0.00888305776570672</v>
+        <v>0.008883057765706718</v>
       </c>
       <c r="AO639" s="190" t="n">
         <v>1930.822146688182</v>
@@ -16097,10 +16097,10 @@
         <v>1.050526065954392</v>
       </c>
       <c r="AN640" s="189" t="n">
-        <v>0.00303948592939519</v>
+        <v>0.003039485929395189</v>
       </c>
       <c r="AO640" s="190" t="n">
-        <v>1759.174773375929</v>
+        <v>1759.174773375928</v>
       </c>
     </row>
     <row r="641">
@@ -16481,7 +16481,7 @@
         <v>0.9981113886434008</v>
       </c>
       <c r="AN656" s="189" t="n">
-        <v>0.002887834600271994</v>
+        <v>0.002887834600271993</v>
       </c>
       <c r="AO656" s="190" t="n">
         <v>511.6942797803975</v>
@@ -16769,7 +16769,7 @@
         <v>0.0714425083209866</v>
       </c>
       <c r="AN668" s="189" t="n">
-        <v>0.0002067045319861345</v>
+        <v>0.0002067045319861344</v>
       </c>
       <c r="AO668" s="190" t="n">
         <v>48.08879897687814</v>
@@ -16817,7 +16817,7 @@
         <v>1.21370812127122</v>
       </c>
       <c r="AN670" s="189" t="n">
-        <v>0.003511620393393175</v>
+        <v>0.003511620393393174</v>
       </c>
       <c r="AO670" s="190" t="n">
         <v>32.82837726414397</v>
@@ -17233,7 +17233,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="159" t="n">
-        <v>2.575059155984192</v>
+        <v>2.575059155984191</v>
       </c>
       <c r="S8" s="160" t="n">
         <v>67.67117291955772</v>
@@ -17255,10 +17255,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="163" t="n">
-        <v>22.90282108124559</v>
+        <v>22.9028210812456</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>65.46234229720311</v>
+        <v>65.46234229720314</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>26812.52920243434</v>
@@ -17280,7 +17280,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>72.51236244952727</v>
+        <v>72.51236244952726</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>70285.35023214569</v>
@@ -17321,7 +17321,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="166" t="n">
-        <v>25.47788023722978</v>
+        <v>25.47788023722979</v>
       </c>
       <c r="S12" s="167" t="n">
         <v>205.6458776662881</v>
@@ -17641,10 +17641,10 @@
         </is>
       </c>
       <c r="P25" s="176" t="n">
-        <v>51479.2874751646</v>
+        <v>51479.28747516461</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.412553976856117</v>
+        <v>0.4125539768561171</v>
       </c>
       <c r="R25" s="176" t="n">
         <v>1200.527210337816</v>
@@ -17734,7 +17734,7 @@
         <v>8.077442965876257</v>
       </c>
       <c r="U26" s="188" t="n">
-        <v>0.02748373899066034</v>
+        <v>0.02748373899066033</v>
       </c>
       <c r="W26" s="184" t="n">
         <v>2</v>
@@ -17809,10 +17809,10 @@
         <v>17044.66297125358</v>
       </c>
       <c r="T27" s="84" t="n">
-        <v>6.942429228798463</v>
+        <v>6.942429228798462</v>
       </c>
       <c r="U27" s="188" t="n">
-        <v>0.023621821124766</v>
+        <v>0.02362182112476599</v>
       </c>
       <c r="W27" s="184" t="n">
         <v>3</v>
@@ -17953,13 +17953,13 @@
         </is>
       </c>
       <c r="P29" s="185" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04614941856286704</v>
+        <v>0.04614941856286705</v>
       </c>
       <c r="R29" s="185" t="n">
-        <v>629.9102787609263</v>
+        <v>629.9102787609264</v>
       </c>
       <c r="S29" s="187" t="n">
         <v>8154.317491039048</v>
@@ -17968,7 +17968,7 @@
         <v>9.141959392549317</v>
       </c>
       <c r="U29" s="188" t="n">
-        <v>0.03110578766937595</v>
+        <v>0.03110578766937594</v>
       </c>
       <c r="W29" s="184" t="n">
         <v>5</v>
@@ -18065,7 +18065,7 @@
         <v>25.9010570595086</v>
       </c>
       <c r="AA30" s="189" t="n">
-        <v>0.0881291139798857</v>
+        <v>0.08812911397988568</v>
       </c>
       <c r="AB30" s="190" t="n">
         <v>36228.8589408932</v>
@@ -18182,7 +18182,7 @@
         <v>6.511948284202157</v>
       </c>
       <c r="U32" s="197" t="n">
-        <v>0.02215709695751163</v>
+        <v>0.02215709695751162</v>
       </c>
       <c r="W32" s="184" t="n">
         <v>8</v>
@@ -18254,7 +18254,7 @@
         <v>665.5266097117527</v>
       </c>
       <c r="S33" s="187" t="n">
-        <v>6781.217652820742</v>
+        <v>6781.217652820743</v>
       </c>
       <c r="T33" s="84" t="n">
         <v>4.775784957707994</v>
@@ -18338,7 +18338,7 @@
         <v>6.402275534841854</v>
       </c>
       <c r="U34" s="197" t="n">
-        <v>0.02178393217868986</v>
+        <v>0.02178393217868985</v>
       </c>
       <c r="W34" s="184" t="n">
         <v>10</v>
@@ -18416,7 +18416,7 @@
         <v>8.077442965876257</v>
       </c>
       <c r="U35" s="197" t="n">
-        <v>0.02748373899066034</v>
+        <v>0.02748373899066033</v>
       </c>
       <c r="W35" s="184" t="n">
         <v>11</v>
@@ -18650,7 +18650,7 @@
         <v>4.864353177656564</v>
       </c>
       <c r="U38" s="197" t="n">
-        <v>0.01655110579646157</v>
+        <v>0.01655110579646156</v>
       </c>
       <c r="W38" s="184" t="n">
         <v>14</v>
@@ -18669,7 +18669,7 @@
         <v>13.39308931175454</v>
       </c>
       <c r="AA38" s="189" t="n">
-        <v>0.04557038316183679</v>
+        <v>0.04557038316183678</v>
       </c>
       <c r="AB38" s="190" t="n">
         <v>8505.25352201269</v>
@@ -18805,7 +18805,7 @@
         <v>1.948394549911982</v>
       </c>
       <c r="AA40" s="189" t="n">
-        <v>0.006629470178474597</v>
+        <v>0.006629470178474595</v>
       </c>
       <c r="AB40" s="190" t="n">
         <v>6403.476994667846</v>
@@ -18866,7 +18866,7 @@
         <v>1.097378278018554</v>
       </c>
       <c r="U41" s="197" t="n">
-        <v>0.003733862101471418</v>
+        <v>0.003733862101471417</v>
       </c>
       <c r="W41" s="184" t="n">
         <v>17</v>
@@ -19045,7 +19045,7 @@
         <v>2.592208925255899</v>
       </c>
       <c r="AA43" s="189" t="n">
-        <v>0.008820067663983144</v>
+        <v>0.008820067663983142</v>
       </c>
       <c r="AB43" s="190" t="n">
         <v>5475.748110272933</v>
@@ -19538,7 +19538,7 @@
         <v>2295.663320808904</v>
       </c>
       <c r="Q52" s="186" t="n">
-        <v>0.08292363527473673</v>
+        <v>0.08292363527473672</v>
       </c>
       <c r="R52" s="185" t="n">
         <v>376.6692492661692</v>
@@ -19613,7 +19613,7 @@
         <v>1922.615466855054</v>
       </c>
       <c r="Q53" s="186" t="n">
-        <v>0.06944845191449026</v>
+        <v>0.06944845191449024</v>
       </c>
       <c r="R53" s="185" t="n">
         <v>277.6932486522649</v>
@@ -19688,7 +19688,7 @@
         <v>1738.127350664389</v>
       </c>
       <c r="Q54" s="186" t="n">
-        <v>0.06278439751206709</v>
+        <v>0.06278439751206707</v>
       </c>
       <c r="R54" s="185" t="n">
         <v>446.6491451135092</v>
@@ -19763,7 +19763,7 @@
         <v>1715.333889106135</v>
       </c>
       <c r="Q55" s="186" t="n">
-        <v>0.06196105522325123</v>
+        <v>0.06196105522325122</v>
       </c>
       <c r="R55" s="185" t="n">
         <v>1563.119959147881</v>
@@ -19838,7 +19838,7 @@
         <v>958.9700902822325</v>
       </c>
       <c r="Q56" s="186" t="n">
-        <v>0.03463978593251424</v>
+        <v>0.03463978593251423</v>
       </c>
       <c r="R56" s="185" t="n">
         <v>294.5263225166185</v>
@@ -20288,7 +20288,7 @@
         <v>329.143363749303</v>
       </c>
       <c r="Q62" s="186" t="n">
-        <v>0.01188927139325898</v>
+        <v>0.01188927139325897</v>
       </c>
       <c r="R62" s="185" t="n">
         <v>152.1155785618588</v>
@@ -20438,7 +20438,7 @@
         <v>246.9408990285878</v>
       </c>
       <c r="Q64" s="186" t="n">
-        <v>0.008919965249192904</v>
+        <v>0.008919965249192901</v>
       </c>
       <c r="R64" s="185" t="n">
         <v>254.6574300969091</v>
@@ -20513,7 +20513,7 @@
         <v>164.3013003104025</v>
       </c>
       <c r="Q65" s="186" t="n">
-        <v>0.005934869010889656</v>
+        <v>0.005934869010889655</v>
       </c>
       <c r="R65" s="185" t="n">
         <v>125.2186189598836</v>
@@ -20589,7 +20589,7 @@
         <v>80.28978246687787</v>
       </c>
       <c r="Q66" s="186" t="n">
-        <v>0.002900216498308356</v>
+        <v>0.002900216498308355</v>
       </c>
       <c r="R66" s="185" t="n">
         <v>18.52354606116344</v>
@@ -21667,10 +21667,10 @@
         </is>
       </c>
       <c r="Z84" s="84" t="n">
-        <v>0.8350262356765638</v>
+        <v>0.8350262356765636</v>
       </c>
       <c r="AA84" s="189" t="n">
-        <v>0.01290321868135387</v>
+        <v>0.01290321868135386</v>
       </c>
       <c r="AB84" s="190" t="n">
         <v>2881.56464760053</v>
@@ -24246,7 +24246,7 @@
         </is>
       </c>
       <c r="O145" s="242" t="n">
-        <v>60099.70267713495</v>
+        <v>60099.70267713496</v>
       </c>
       <c r="P145" s="72" t="n">
         <v>49.86769475813242</v>
@@ -24273,10 +24273,10 @@
         <v>26967.75168511963</v>
       </c>
       <c r="P146" s="84" t="n">
-        <v>26.54016974502199</v>
+        <v>26.54016974502198</v>
       </c>
       <c r="Q146" s="84" t="n">
-        <v>26.54016974502199</v>
+        <v>26.54016974502198</v>
       </c>
       <c r="R146" s="245" t="n">
         <v>45477.57121251606</v>
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="O299" s="242" t="n">
-        <v>60099.70267713495</v>
+        <v>60099.70267713496</v>
       </c>
       <c r="P299" s="72" t="n">
         <v>49.86769475813242</v>
@@ -26729,10 +26729,10 @@
         <v>26967.75168511963</v>
       </c>
       <c r="P300" s="84" t="n">
-        <v>26.54016974502199</v>
+        <v>26.54016974502198</v>
       </c>
       <c r="Q300" s="84" t="n">
-        <v>26.54016974502199</v>
+        <v>26.54016974502198</v>
       </c>
       <c r="R300" s="245" t="n">
         <v>45477.57121251606</v>
@@ -30393,7 +30393,7 @@
         <v>25.9010570595086</v>
       </c>
       <c r="AN612" s="189" t="n">
-        <v>0.0881291139798857</v>
+        <v>0.08812911397988568</v>
       </c>
       <c r="AO612" s="190" t="n">
         <v>36228.8589408932</v>
@@ -30585,7 +30585,7 @@
         <v>13.39308931175454</v>
       </c>
       <c r="AN620" s="189" t="n">
-        <v>0.04557038316183679</v>
+        <v>0.04557038316183678</v>
       </c>
       <c r="AO620" s="190" t="n">
         <v>8505.25352201269</v>
@@ -30633,7 +30633,7 @@
         <v>1.948394549911982</v>
       </c>
       <c r="AN622" s="189" t="n">
-        <v>0.006629470178474597</v>
+        <v>0.006629470178474595</v>
       </c>
       <c r="AO622" s="190" t="n">
         <v>6403.476994667846</v>
@@ -30705,7 +30705,7 @@
         <v>2.592208925255899</v>
       </c>
       <c r="AN625" s="189" t="n">
-        <v>0.008820067663983144</v>
+        <v>0.008820067663983142</v>
       </c>
       <c r="AO625" s="190" t="n">
         <v>5475.748110272933</v>
@@ -30801,7 +30801,7 @@
         <v>1.99057346682708</v>
       </c>
       <c r="AN629" s="189" t="n">
-        <v>0.006772985192854836</v>
+        <v>0.006772985192854835</v>
       </c>
       <c r="AO629" s="190" t="n">
         <v>4202.675151630569</v>
@@ -31209,7 +31209,7 @@
         <v>1.33591344695991</v>
       </c>
       <c r="AN646" s="189" t="n">
-        <v>0.004545485080546963</v>
+        <v>0.004545485080546962</v>
       </c>
       <c r="AO646" s="190" t="n">
         <v>1120.160331729499</v>
@@ -31257,7 +31257,7 @@
         <v>4.570527344069708</v>
       </c>
       <c r="AN648" s="189" t="n">
-        <v>0.01555135469290942</v>
+        <v>0.01555135469290941</v>
       </c>
       <c r="AO648" s="190" t="n">
         <v>901.8171175743003</v>
@@ -31329,7 +31329,7 @@
         <v>1.185378011352536</v>
       </c>
       <c r="AN651" s="189" t="n">
-        <v>0.004033283801187064</v>
+        <v>0.004033283801187063</v>
       </c>
       <c r="AO651" s="190" t="n">
         <v>674.3035107796646</v>
@@ -31449,7 +31449,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="AN656" s="189" t="n">
-        <v>0.003386492596427418</v>
+        <v>0.003386492596427417</v>
       </c>
       <c r="AO656" s="190" t="n">
         <v>535.75849421705</v>
@@ -31497,7 +31497,7 @@
         <v>0.1797265991720041</v>
       </c>
       <c r="AN658" s="189" t="n">
-        <v>0.0006115250781949084</v>
+        <v>0.0006115250781949081</v>
       </c>
       <c r="AO658" s="190" t="n">
         <v>402.1661877448232</v>
@@ -31641,7 +31641,7 @@
         <v>0.1377616586356387</v>
       </c>
       <c r="AN664" s="189" t="n">
-        <v>0.000468738124782489</v>
+        <v>0.0004687381247824889</v>
       </c>
       <c r="AO664" s="190" t="n">
         <v>135.8295374124733</v>
@@ -31833,7 +31833,7 @@
         <v>1.312115575743891</v>
       </c>
       <c r="AN672" s="189" t="n">
-        <v>0.004464512118707736</v>
+        <v>0.004464512118707735</v>
       </c>
       <c r="AO672" s="190" t="n">
         <v>37.2646071973568</v>
@@ -31929,7 +31929,7 @@
         <v>0.02031495125115925</v>
       </c>
       <c r="AN676" s="189" t="n">
-        <v>6.912222347512182e-05</v>
+        <v>6.912222347512181e-05</v>
       </c>
       <c r="AO676" s="190" t="n">
         <v>14.30886932257346</v>
@@ -32280,7 +32280,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>73.77876919115965</v>
+        <v>73.77876919115967</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>28828.09121400122</v>
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>81792.70862910869</v>
+        <v>81792.7086291087</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -32302,7 +32302,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>105.5668724914504</v>
+        <v>105.5668724914503</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>81898.27550160015</v>
@@ -32663,19 +32663,19 @@
         </is>
       </c>
       <c r="P25" s="176" t="n">
-        <v>64043.47173804005</v>
+        <v>64043.47173804007</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.4629072339112968</v>
+        <v>0.462907233911297</v>
       </c>
       <c r="R25" s="176" t="n">
-        <v>1245.565925394592</v>
+        <v>1245.565925394593</v>
       </c>
       <c r="S25" s="178" t="n">
         <v>122033.8634974797</v>
       </c>
       <c r="T25" s="72" t="n">
-        <v>51.41716743555845</v>
+        <v>51.41716743555844</v>
       </c>
       <c r="U25" s="179" t="n">
         <v>0.2141700184075503</v>
@@ -32853,7 +32853,7 @@
         <v>3.273092722030352</v>
       </c>
       <c r="AA27" s="189" t="n">
-        <v>0.01363354621596816</v>
+        <v>0.01363354621596817</v>
       </c>
       <c r="AB27" s="190" t="n">
         <v>87013.41101186405</v>
@@ -32981,13 +32981,13 @@
         <v>0.04371550946638431</v>
       </c>
       <c r="R29" s="185" t="n">
-        <v>661.2546573048478</v>
+        <v>661.2546573048479</v>
       </c>
       <c r="S29" s="187" t="n">
         <v>8366.076003824408</v>
       </c>
       <c r="T29" s="84" t="n">
-        <v>9.146347533057741</v>
+        <v>9.146347533057739</v>
       </c>
       <c r="U29" s="188" t="n">
         <v>0.03809765331728747</v>
@@ -33457,7 +33457,7 @@
         <v>9.393915268543527</v>
       </c>
       <c r="AA35" s="189" t="n">
-        <v>0.03912885727329222</v>
+        <v>0.03912885727329223</v>
       </c>
       <c r="AB35" s="190" t="n">
         <v>9991.719500892608</v>
@@ -33736,7 +33736,7 @@
         <v>3.148664098804754</v>
       </c>
       <c r="U39" s="197" t="n">
-        <v>0.01311525861173458</v>
+        <v>0.01311525861173459</v>
       </c>
       <c r="W39" s="184" t="n">
         <v>15</v>
@@ -33827,7 +33827,7 @@
         <v>10.38270607772277</v>
       </c>
       <c r="AA40" s="189" t="n">
-        <v>0.04324750784011987</v>
+        <v>0.04324750784011989</v>
       </c>
       <c r="AB40" s="190" t="n">
         <v>6830.803358594248</v>
@@ -34128,7 +34128,7 @@
         <v>1.329196099991223</v>
       </c>
       <c r="U44" s="209" t="n">
-        <v>0.005536554567288221</v>
+        <v>0.005536554567288222</v>
       </c>
       <c r="W44" s="205" t="n">
         <v>20</v>
@@ -36530,10 +36530,10 @@
         </is>
       </c>
       <c r="Z81" s="84" t="n">
-        <v>2.254539664450447</v>
+        <v>2.254539664450446</v>
       </c>
       <c r="AA81" s="189" t="n">
-        <v>0.04328168216573708</v>
+        <v>0.04328168216573707</v>
       </c>
       <c r="AB81" s="190" t="n">
         <v>4100.724704907474</v>
@@ -36583,7 +36583,7 @@
         </is>
       </c>
       <c r="Z82" s="84" t="n">
-        <v>1.002031482811876</v>
+        <v>1.002031482811877</v>
       </c>
       <c r="AA82" s="189" t="n">
         <v>0.01923656915111201</v>
@@ -37326,7 +37326,7 @@
         <v>25.78760964056661</v>
       </c>
       <c r="U97" s="213" t="n">
-        <v>0.2978492945753625</v>
+        <v>0.2978492945753626</v>
       </c>
       <c r="W97" s="175" t="n">
         <v>1</v>
@@ -39661,7 +39661,7 @@
         <v>1.947948910730224</v>
       </c>
       <c r="R161" s="245" t="n">
-        <v>6340.972676806965</v>
+        <v>6340.972676806964</v>
       </c>
       <c r="T161" s="172" t="n"/>
       <c r="U161" s="172" t="n"/>
@@ -39733,7 +39733,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="245" t="n">
-        <v>549334.6926502126</v>
+        <v>549334.6926502124</v>
       </c>
       <c r="T164" s="172" t="n"/>
       <c r="U164" s="172" t="n"/>
@@ -42087,7 +42087,7 @@
         <v>1.947948910730224</v>
       </c>
       <c r="R315" s="245" t="n">
-        <v>6340.972676806965</v>
+        <v>6340.972676806964</v>
       </c>
     </row>
     <row r="316">
@@ -43815,7 +43815,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="243" t="n">
-        <v>549334.6926502126</v>
+        <v>549334.6926502124</v>
       </c>
     </row>
     <row r="454">
@@ -45343,7 +45343,7 @@
         <v>3.273092722030352</v>
       </c>
       <c r="AN609" s="189" t="n">
-        <v>0.01363354621596816</v>
+        <v>0.01363354621596817</v>
       </c>
       <c r="AO609" s="190" t="n">
         <v>87013.41101186405</v>
@@ -45535,7 +45535,7 @@
         <v>9.393915268543527</v>
       </c>
       <c r="AN617" s="189" t="n">
-        <v>0.03912885727329222</v>
+        <v>0.03912885727329223</v>
       </c>
       <c r="AO617" s="190" t="n">
         <v>9991.719500892608</v>
@@ -45655,7 +45655,7 @@
         <v>10.38270607772277</v>
       </c>
       <c r="AN622" s="189" t="n">
-        <v>0.04324750784011987</v>
+        <v>0.04324750784011989</v>
       </c>
       <c r="AO622" s="190" t="n">
         <v>6830.803358594248</v>
@@ -45775,7 +45775,7 @@
         <v>4.490616967686024</v>
       </c>
       <c r="AN627" s="189" t="n">
-        <v>0.01870494946723678</v>
+        <v>0.01870494946723679</v>
       </c>
       <c r="AO627" s="190" t="n">
         <v>5028.408937422466</v>
@@ -45823,7 +45823,7 @@
         <v>1.980998808451642</v>
       </c>
       <c r="AN629" s="189" t="n">
-        <v>0.008251534894510963</v>
+        <v>0.008251534894510965</v>
       </c>
       <c r="AO629" s="190" t="n">
         <v>4359.951351229753</v>
@@ -46159,7 +46159,7 @@
         <v>0.7213698454122264</v>
       </c>
       <c r="AN643" s="189" t="n">
-        <v>0.00300475115172805</v>
+        <v>0.003004751151728051</v>
       </c>
       <c r="AO643" s="190" t="n">
         <v>1251.563120782912</v>
@@ -46399,7 +46399,7 @@
         <v>0.2066855890478047</v>
       </c>
       <c r="AN653" s="189" t="n">
-        <v>0.0008609158889668991</v>
+        <v>0.0008609158889668993</v>
       </c>
       <c r="AO653" s="190" t="n">
         <v>474.0533938042103</v>
@@ -46447,7 +46447,7 @@
         <v>0.2186062166351055</v>
       </c>
       <c r="AN655" s="189" t="n">
-        <v>0.0009105693638107152</v>
+        <v>0.0009105693638107155</v>
       </c>
       <c r="AO655" s="190" t="n">
         <v>368.9107410613797</v>
@@ -46471,7 +46471,7 @@
         <v>0.3861512108415192</v>
       </c>
       <c r="AN656" s="189" t="n">
-        <v>0.001608451341425548</v>
+        <v>0.001608451341425549</v>
       </c>
       <c r="AO656" s="190" t="n">
         <v>339.8745718075103</v>
@@ -46831,7 +46831,7 @@
         <v>1.40351754675021</v>
       </c>
       <c r="AN671" s="189" t="n">
-        <v>0.005846128711768223</v>
+        <v>0.005846128711768225</v>
       </c>
       <c r="AO671" s="190" t="n">
         <v>41.85348272146092</v>
@@ -47315,7 +47315,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>91166.48433398565</v>
+        <v>91166.48433398562</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -47327,7 +47327,7 @@
         <v>182.81988662555</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>91349.3042206112</v>
+        <v>91349.30422061117</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -47359,7 +47359,7 @@
         </is>
       </c>
       <c r="P12" s="165" t="n">
-        <v>146831.7406457918</v>
+        <v>146831.7406457917</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>0</v>
@@ -47368,7 +47368,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>276.6841221167718</v>
+        <v>276.6841221167719</v>
       </c>
       <c r="T12" s="168" t="n">
         <v>147108.4247679085</v>
@@ -47688,7 +47688,7 @@
         <v>78816.00626191396</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.5357681341925942</v>
+        <v>0.5357681341925943</v>
       </c>
       <c r="R25" s="176" t="n">
         <v>1278.180270252493</v>
@@ -47766,7 +47766,7 @@
         <v>11957.11386915134</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.08128095918378539</v>
+        <v>0.08128095918378542</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>1352.765962052527</v>
@@ -47844,7 +47844,7 @@
         <v>8676.100013225549</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.0589775876324809</v>
+        <v>0.05897758763248091</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>1356.034136040362</v>
@@ -47922,7 +47922,7 @@
         <v>7177.156153383478</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.0487882061459553</v>
+        <v>0.04878820614595532</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>1420.976010268078</v>
@@ -47997,19 +47997,19 @@
         </is>
       </c>
       <c r="P29" s="185" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="Q29" s="186" t="n">
         <v>0.0425163782334069</v>
       </c>
       <c r="R29" s="185" t="n">
-        <v>686.0358204215186</v>
+        <v>686.0358204215183</v>
       </c>
       <c r="S29" s="187" t="n">
         <v>8526.973997461853</v>
       </c>
       <c r="T29" s="84" t="n">
-        <v>9.116896294001295</v>
+        <v>9.116896294001297</v>
       </c>
       <c r="U29" s="188" t="n">
         <v>0.04017202535503294</v>
@@ -48142,7 +48142,7 @@
         <v>4549.550472108819</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.03092651205589754</v>
+        <v>0.03092651205589755</v>
       </c>
       <c r="R31" s="185" t="n">
         <v>0</v>
@@ -48214,7 +48214,7 @@
         <v>4549.550472108819</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.03092651205589754</v>
+        <v>0.03092651205589755</v>
       </c>
       <c r="R32" s="185" t="n">
         <v>0</v>
@@ -48292,7 +48292,7 @@
         <v>4469.377130929079</v>
       </c>
       <c r="Q33" s="186" t="n">
-        <v>0.03038151715634485</v>
+        <v>0.03038151715634486</v>
       </c>
       <c r="R33" s="185" t="n">
         <v>653.2124194089411</v>
@@ -48560,7 +48560,7 @@
         <v>0.0123627791674595</v>
       </c>
       <c r="AB36" s="190" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -48604,7 +48604,7 @@
         <v>1374.07878237639</v>
       </c>
       <c r="Q37" s="186" t="n">
-        <v>0.009340585248902366</v>
+        <v>0.009340585248902368</v>
       </c>
       <c r="R37" s="185" t="n">
         <v>215.3316853088869</v>
@@ -48682,7 +48682,7 @@
         <v>1208.641034384585</v>
       </c>
       <c r="Q38" s="186" t="n">
-        <v>0.008215987876231059</v>
+        <v>0.008215987876231061</v>
       </c>
       <c r="R38" s="185" t="n">
         <v>0</v>
@@ -48746,7 +48746,7 @@
         <v>1156.497538676922</v>
       </c>
       <c r="Q39" s="186" t="n">
-        <v>0.007861531659396915</v>
+        <v>0.007861531659396917</v>
       </c>
       <c r="R39" s="185" t="n">
         <v>0</v>
@@ -48818,7 +48818,7 @@
         <v>884.4130782099252</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.006011981160190211</v>
+        <v>0.006011981160190213</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>449.9758725135909</v>
@@ -48898,7 +48898,7 @@
         <v>813.7050826922497</v>
       </c>
       <c r="Q41" s="186" t="n">
-        <v>0.005531328909109209</v>
+        <v>0.005531328909109211</v>
       </c>
       <c r="R41" s="185" t="n">
         <v>346.1316318614575</v>
@@ -51426,7 +51426,7 @@
         <v>0.02343468482370703</v>
       </c>
       <c r="AB81" s="190" t="n">
-        <v>4334.929426567818</v>
+        <v>4334.929426567819</v>
       </c>
     </row>
     <row r="82">
@@ -51937,7 +51937,7 @@
         <v>0.01420981253888055</v>
       </c>
       <c r="AB91" s="190" t="n">
-        <v>1326.15589090054</v>
+        <v>1326.155890900541</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" thickBot="1">
@@ -52204,7 +52204,7 @@
         <v>51082.33343448647</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.55919783812607</v>
+        <v>0.5591978381260703</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1652.764885833379</v>
@@ -52313,7 +52313,7 @@
         <v>0</v>
       </c>
       <c r="AB98" s="190" t="n">
-        <v>9367.106546647334</v>
+        <v>9367.106546647332</v>
       </c>
     </row>
     <row r="99">
@@ -52354,7 +52354,7 @@
         <v>7233.700896317213</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.07918725772500267</v>
+        <v>0.07918725772500269</v>
       </c>
       <c r="R99" s="185" t="n">
         <v>1297.697205715482</v>
@@ -52429,7 +52429,7 @@
         <v>4549.550472108819</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.04980388751644483</v>
+        <v>0.04980388751644484</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>0</v>
@@ -52504,7 +52504,7 @@
         <v>4549.550472108819</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.04980388751644483</v>
+        <v>0.04980388751644484</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>0</v>
@@ -52579,7 +52579,7 @@
         <v>4221.639102178104</v>
       </c>
       <c r="Q102" s="186" t="n">
-        <v>0.04621424474107349</v>
+        <v>0.04621424474107351</v>
       </c>
       <c r="R102" s="185" t="n">
         <v>1114.43358344224</v>
@@ -52655,7 +52655,7 @@
         <v>3352.032848196808</v>
       </c>
       <c r="Q103" s="186" t="n">
-        <v>0.03669467301142822</v>
+        <v>0.03669467301142824</v>
       </c>
       <c r="R103" s="185" t="n">
         <v>979.8186291134114</v>
@@ -52730,7 +52730,7 @@
         <v>1374.07878237639</v>
       </c>
       <c r="Q104" s="186" t="n">
-        <v>0.0150420278961069</v>
+        <v>0.01504202789610691</v>
       </c>
       <c r="R104" s="185" t="n">
         <v>215.3316853088869</v>
@@ -52955,7 +52955,7 @@
         <v>1062.089576335949</v>
       </c>
       <c r="Q107" s="186" t="n">
-        <v>0.01162668490359786</v>
+        <v>0.01162668490359787</v>
       </c>
       <c r="R107" s="185" t="n">
         <v>0</v>
@@ -53030,7 +53030,7 @@
         <v>462.6481613342091</v>
       </c>
       <c r="Q108" s="186" t="n">
-        <v>0.005064605201774723</v>
+        <v>0.005064605201774724</v>
       </c>
       <c r="R108" s="185" t="n">
         <v>146.6302991118768</v>
@@ -53105,7 +53105,7 @@
         <v>424.8362177620434</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.004650678200416849</v>
+        <v>0.004650678200416851</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>336.4463923211698</v>
@@ -53180,7 +53180,7 @@
         <v>414.2601622668717</v>
       </c>
       <c r="Q110" s="186" t="n">
-        <v>0.004534902217387682</v>
+        <v>0.004534902217387684</v>
       </c>
       <c r="R110" s="185" t="n">
         <v>0</v>
@@ -53235,7 +53235,7 @@
         <v>63.64211364413745</v>
       </c>
       <c r="Q111" s="186" t="n">
-        <v>0.0006966896375087862</v>
+        <v>0.0006966896375087863</v>
       </c>
       <c r="R111" s="185" t="n">
         <v>1544.930224778733</v>
@@ -54117,10 +54117,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R145" s="243" t="n">
         <v>164416.923215098</v>
@@ -54601,7 +54601,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="245" t="n">
-        <v>84134.14986010657</v>
+        <v>84134.14986010658</v>
       </c>
       <c r="T166" s="172" t="n"/>
       <c r="U166" s="172" t="n"/>
@@ -54780,7 +54780,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="245" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
       <c r="T174" s="172" t="n"/>
       <c r="U174" s="172" t="n"/>
@@ -55051,7 +55051,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="245" t="n">
-        <v>4933.735211317694</v>
+        <v>4933.735211317693</v>
       </c>
       <c r="T188" s="172" t="n"/>
       <c r="U188" s="172" t="n"/>
@@ -56575,10 +56575,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R299" s="243" t="n">
         <v>164416.923215098</v>
@@ -56951,7 +56951,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="245" t="n">
-        <v>84134.14986010657</v>
+        <v>84134.14986010658</v>
       </c>
     </row>
     <row r="318">
@@ -57092,7 +57092,7 @@
         <v>0</v>
       </c>
       <c r="R324" s="245" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="325">
@@ -57313,7 +57313,7 @@
         <v>0</v>
       </c>
       <c r="R337" s="245" t="n">
-        <v>4933.735211317694</v>
+        <v>4933.735211317693</v>
       </c>
     </row>
     <row r="338">
@@ -60408,7 +60408,7 @@
         <v>0.0123627791674595</v>
       </c>
       <c r="AO618" s="190" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="619">
@@ -62251,7 +62251,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>95637.05381006612</v>
+        <v>95637.05381006611</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -62263,7 +62263,7 @@
         <v>325.6288357106168</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>95962.68264577673</v>
+        <v>95962.68264577672</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -62621,13 +62621,13 @@
         </is>
       </c>
       <c r="P25" s="176" t="n">
-        <v>97701.03174199554</v>
+        <v>97701.03174199555</v>
       </c>
       <c r="Q25" s="177" t="n">
         <v>0.6355665679026942</v>
       </c>
       <c r="R25" s="176" t="n">
-        <v>1322.000815884655</v>
+        <v>1322.000815884656</v>
       </c>
       <c r="S25" s="178" t="n">
         <v>178793.5289474547</v>
@@ -62714,7 +62714,7 @@
         <v>5.914021765449531</v>
       </c>
       <c r="U26" s="188" t="n">
-        <v>0.02680170169355148</v>
+        <v>0.02680170169355147</v>
       </c>
       <c r="W26" s="184" t="n">
         <v>2</v>
@@ -62889,7 +62889,7 @@
         <v>3.129787432848779</v>
       </c>
       <c r="AA28" s="189" t="n">
-        <v>9.055410591358674e-05</v>
+        <v>9.055410591358673e-05</v>
       </c>
       <c r="AB28" s="190" t="n">
         <v>79098.00518389465</v>
@@ -63045,7 +63045,7 @@
         <v>22.97068657334675</v>
       </c>
       <c r="AA30" s="189" t="n">
-        <v>0.0006646106259610474</v>
+        <v>0.0006646106259610473</v>
       </c>
       <c r="AB30" s="190" t="n">
         <v>32130.03089909558</v>
@@ -63090,7 +63090,7 @@
         <v>9.087539887934609</v>
       </c>
       <c r="U31" s="197" t="n">
-        <v>0.04118373973995008</v>
+        <v>0.04118373973995007</v>
       </c>
       <c r="W31" s="184" t="n">
         <v>7</v>
@@ -63396,7 +63396,7 @@
         <v>6.900842370196097</v>
       </c>
       <c r="U35" s="197" t="n">
-        <v>0.0312738650575727</v>
+        <v>0.03127386505757269</v>
       </c>
       <c r="W35" s="184" t="n">
         <v>11</v>
@@ -63474,7 +63474,7 @@
         <v>1.950058510415481</v>
       </c>
       <c r="U36" s="197" t="n">
-        <v>0.008837452507609152</v>
+        <v>0.00883745250760915</v>
       </c>
       <c r="W36" s="184" t="n">
         <v>12</v>
@@ -63552,7 +63552,7 @@
         <v>1.503942641298857</v>
       </c>
       <c r="U37" s="197" t="n">
-        <v>0.006815704039472704</v>
+        <v>0.006815704039472703</v>
       </c>
       <c r="W37" s="184" t="n">
         <v>13</v>
@@ -63766,7 +63766,7 @@
         <v>1.352119189989452</v>
       </c>
       <c r="U40" s="197" t="n">
-        <v>0.006127656715086366</v>
+        <v>0.006127656715086365</v>
       </c>
       <c r="W40" s="184" t="n">
         <v>16</v>
@@ -63785,7 +63785,7 @@
         <v>13.03311468417755</v>
       </c>
       <c r="AA40" s="189" t="n">
-        <v>0.0003770869660693535</v>
+        <v>0.0003770869660693534</v>
       </c>
       <c r="AB40" s="190" t="n">
         <v>7972.278752690054</v>
@@ -64063,7 +64063,7 @@
         <v>2.411334708752383</v>
       </c>
       <c r="AA44" s="210" t="n">
-        <v>6.976712102480391e-05</v>
+        <v>6.976712102480389e-05</v>
       </c>
       <c r="AB44" s="211" t="n">
         <v>4972.608658942901</v>
@@ -66997,10 +66997,10 @@
         <v>115799.3123637093</v>
       </c>
       <c r="T97" s="72" t="n">
-        <v>36.99734860949913</v>
+        <v>36.99734860949912</v>
       </c>
       <c r="U97" s="213" t="n">
-        <v>0.4516533505179703</v>
+        <v>0.4516533505179702</v>
       </c>
       <c r="W97" s="175" t="n">
         <v>1</v>
@@ -67063,7 +67063,7 @@
         <v>6982.4185824382</v>
       </c>
       <c r="Q98" s="186" t="n">
-        <v>0.07276181104911507</v>
+        <v>0.07276181104911508</v>
       </c>
       <c r="R98" s="185" t="n">
         <v>0</v>
@@ -67138,7 +67138,7 @@
         <v>6982.4185824382</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.07276181104911507</v>
+        <v>0.07276181104911508</v>
       </c>
       <c r="R99" s="185" t="n">
         <v>0</v>
@@ -67288,7 +67288,7 @@
         <v>5971.172990159375</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.06222390647623442</v>
+        <v>0.06222390647623443</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>1208.826425409853</v>
@@ -67439,7 +67439,7 @@
         <v>1572.67432362361</v>
       </c>
       <c r="Q103" s="186" t="n">
-        <v>0.01638839474120123</v>
+        <v>0.01638839474120124</v>
       </c>
       <c r="R103" s="185" t="n">
         <v>227.8959928741164</v>
@@ -67589,7 +67589,7 @@
         <v>466.9867617082518</v>
       </c>
       <c r="Q105" s="186" t="n">
-        <v>0.004866337088887162</v>
+        <v>0.004866337088887163</v>
       </c>
       <c r="R105" s="185" t="n">
         <v>353.5362999423786</v>
@@ -68904,7 +68904,7 @@
         </is>
       </c>
       <c r="O148" s="244" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P148" s="84" t="n">
         <v>9.087539887934609</v>
@@ -69509,7 +69509,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="245" t="n">
-        <v>6326.659044536187</v>
+        <v>6326.659044536188</v>
       </c>
       <c r="T175" s="172" t="n"/>
       <c r="U175" s="172" t="n"/>
@@ -69584,7 +69584,7 @@
         <v>0</v>
       </c>
       <c r="P180" s="84" t="n">
-        <v>0.1101668065004472</v>
+        <v>0.1101668065004473</v>
       </c>
       <c r="Q180" s="84" t="n">
         <v>0</v>
@@ -69826,7 +69826,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="245" t="n">
-        <v>2369.932679494436</v>
+        <v>2369.932679494435</v>
       </c>
       <c r="T192" s="172" t="n"/>
       <c r="U192" s="172" t="n"/>
@@ -70090,7 +70090,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="245" t="n">
-        <v>526.9557522630023</v>
+        <v>526.9557522630022</v>
       </c>
       <c r="T203" s="172" t="n"/>
       <c r="U203" s="172" t="n"/>
@@ -71356,7 +71356,7 @@
         </is>
       </c>
       <c r="O302" s="244" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P302" s="84" t="n">
         <v>9.087539887934609</v>
@@ -71797,7 +71797,7 @@
         <v>0</v>
       </c>
       <c r="R324" s="245" t="n">
-        <v>6326.659044536187</v>
+        <v>6326.659044536188</v>
       </c>
     </row>
     <row r="325">
@@ -71862,7 +71862,7 @@
         <v>0</v>
       </c>
       <c r="P329" s="84" t="n">
-        <v>0.1101668065004472</v>
+        <v>0.1101668065004473</v>
       </c>
       <c r="Q329" s="84" t="n">
         <v>0</v>
@@ -72080,7 +72080,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="245" t="n">
-        <v>2369.932679494436</v>
+        <v>2369.932679494435</v>
       </c>
     </row>
     <row r="342">
@@ -72322,7 +72322,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="245" t="n">
-        <v>526.9557522630023</v>
+        <v>526.9557522630022</v>
       </c>
     </row>
     <row r="353">
@@ -75363,7 +75363,7 @@
         <v>1.950058510415481</v>
       </c>
       <c r="AN628" s="189" t="n">
-        <v>0.008837452507609152</v>
+        <v>0.00883745250760915</v>
       </c>
       <c r="AO628" s="190" t="n">
         <v>4619.673003586521</v>
@@ -75507,7 +75507,7 @@
         <v>3.123631353199159</v>
       </c>
       <c r="AN634" s="189" t="n">
-        <v>0.01415595664834434</v>
+        <v>0.01415595664834433</v>
       </c>
       <c r="AO634" s="190" t="n">
         <v>2146.93311562612</v>
@@ -75675,7 +75675,7 @@
         <v>1.561228801177662</v>
       </c>
       <c r="AN641" s="189" t="n">
-        <v>0.007075318668761124</v>
+        <v>0.007075318668761123</v>
       </c>
       <c r="AO641" s="190" t="n">
         <v>1660.581324415185</v>
@@ -75963,7 +75963,7 @@
         <v>0.9750292552077404</v>
       </c>
       <c r="AN653" s="189" t="n">
-        <v>0.004418726253804576</v>
+        <v>0.004418726253804575</v>
       </c>
       <c r="AO653" s="190" t="n">
         <v>607.5840912893663</v>
@@ -75987,7 +75987,7 @@
         <v>1.024183284325267</v>
       </c>
       <c r="AN654" s="189" t="n">
-        <v>0.00464148695332391</v>
+        <v>0.004641486953323909</v>
       </c>
       <c r="AO654" s="190" t="n">
         <v>566.0803278713886</v>
@@ -76155,7 +76155,7 @@
         <v>0.5147254320508424</v>
       </c>
       <c r="AN661" s="189" t="n">
-        <v>0.002332679525210112</v>
+        <v>0.002332679525210111</v>
       </c>
       <c r="AO661" s="190" t="n">
         <v>361.7014487446324</v>
@@ -76299,7 +76299,7 @@
         <v>0.1651401069926163</v>
       </c>
       <c r="AN667" s="189" t="n">
-        <v>0.0007483969557086757</v>
+        <v>0.0007483969557086756</v>
       </c>
       <c r="AO667" s="190" t="n">
         <v>234.4852246581214</v>
@@ -76395,7 +76395,7 @@
         <v>0.1101668065004472</v>
       </c>
       <c r="AN671" s="189" t="n">
-        <v>0.0004992639529340251</v>
+        <v>0.000499263952934025</v>
       </c>
       <c r="AO671" s="190" t="n">
         <v>127.6171853505406</v>
@@ -76779,7 +76779,7 @@
         <v>0.01454768030557474</v>
       </c>
       <c r="AN687" s="189" t="n">
-        <v>6.592850066278564e-05</v>
+        <v>6.592850066278563e-05</v>
       </c>
       <c r="AO687" s="190" t="n">
         <v>11.65062397861912</v>
